--- a/data/cci/cci-platform-sensor-mapping.xlsx
+++ b/data/cci/cci-platform-sensor-mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{8B2F088A-9769-4193-994F-31B65C95E3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9666F9D4-58BB-4BBA-AD2C-E382D7D9F66B}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{8B2F088A-9769-4193-994F-31B65C95E3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D14B4A-B9AE-4419-938A-69A22C57ABCF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{FD923E19-B480-F145-8CDB-DB01416B5D33}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="34515" windowHeight="15285" xr2:uid="{FD923E19-B480-F145-8CDB-DB01416B5D33}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="235">
   <si>
     <t>Platform URI</t>
   </si>
@@ -718,6 +718,15 @@
   </si>
   <si>
     <t>sens_mopitt</t>
+  </si>
+  <si>
+    <t>plat_himawari8</t>
+  </si>
+  <si>
+    <t>sens_ahi</t>
+  </si>
+  <si>
+    <t>plat_himawari9</t>
   </si>
 </sst>
 </file>
@@ -727,7 +736,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$£-809]#,##0.00;[Red]&quot;-&quot;[$£-809]#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -832,6 +841,11 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2364,7 +2378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D23046F-D1C9-1F4C-9DE5-3EC2595819A2}">
-  <dimension ref="A1:D204"/>
+  <dimension ref="A1:D206"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -5231,7 +5245,36 @@
         <v>7</v>
       </c>
     </row>
+    <row r="205" spans="1:4">
+      <c r="A205" t="s">
+        <v>232</v>
+      </c>
+      <c r="B205" t="s">
+        <v>5</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D205" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
+        <v>234</v>
+      </c>
+      <c r="B206" t="s">
+        <v>5</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D206" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C24" r:id="rId1" xr:uid="{A4307767-F8FE-F744-AB82-BB91E462188A}"/>
     <hyperlink ref="C28" r:id="rId2" xr:uid="{4D49CAF7-CDB1-3449-8581-C9ED7766EBB0}"/>
